--- a/CollectaMundo/TestFiles/Book1.xlsx
+++ b/CollectaMundo/TestFiles/Book1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\code\CollectaMundo\CollectaMundo\TestFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BD7F96D2-ED6E-456E-8381-4CB5376F0067}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B8E200B-ACDB-4445-A4A4-D185EAA19EBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{FFDDD5DE-D46E-48E6-B24F-65BAAF47E86B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{FFDDD5DE-D46E-48E6-B24F-65BAAF47E86B}"/>
   </bookViews>
   <sheets>
     <sheet name="view_allCards" sheetId="1" r:id="rId1"/>
@@ -2898,27 +2898,12 @@
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{656F986C-225C-4F79-A7D6-053249FD50D8}" name="Table1" displayName="Table1" ref="A1:V60" totalsRowShown="0">
   <autoFilter ref="A1:V60" xr:uid="{656F986C-225C-4F79-A7D6-053249FD50D8}">
-    <filterColumn colId="7">
+    <filterColumn colId="6">
       <filters>
-        <filter val="G"/>
-        <filter val="G, U"/>
-        <filter val="R"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters>
-        <filter val="2.0"/>
-        <filter val="3.0"/>
-        <filter val="4.0"/>
-        <filter val="5.0"/>
-        <filter val="6.0"/>
-        <filter val="7.0"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="18">
-      <filters>
-        <filter val="common"/>
-        <filter val="uncommon"/>
+        <filter val="Artifact, Creature"/>
+        <filter val="Creature"/>
+        <filter val="Planeswalker"/>
+        <filter val="Token, Creature"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -2953,25 +2938,10 @@
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{5038B013-55FD-4B94-A2EF-F507FC8588B5}" name="Table4" displayName="Table4" ref="A1:AA23" totalsRowShown="0">
   <autoFilter ref="A1:AA23" xr:uid="{5038B013-55FD-4B94-A2EF-F507FC8588B5}">
-    <filterColumn colId="7">
+    <filterColumn colId="6">
       <filters>
-        <filter val="G"/>
-        <filter val="R"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="13">
-      <filters>
-        <filter val="2.0"/>
-        <filter val="3.0"/>
-        <filter val="4.0"/>
-        <filter val="5.0"/>
-        <filter val="6.0"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="23">
-      <filters>
-        <filter val="common"/>
-        <filter val="uncommon"/>
+        <filter val="Artifact, Creature"/>
+        <filter val="Creature"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -3154,7 +3124,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office-tema">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -3470,7 +3440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4587AF0-0602-4C7C-9D3A-09A3F75E1D40}">
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:V65"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="49.42578125" bestFit="1" customWidth="1"/>
@@ -3478,14 +3448,14 @@
     <col min="3" max="3" width="14.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.85546875" customWidth="1"/>
     <col min="5" max="5" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="7" max="7" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="36" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="23.28515625" customWidth="1"/>
+    <col min="13" max="13" width="94.28515625" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="38.140625" bestFit="1" customWidth="1"/>
@@ -3497,7 +3467,7 @@
     <col min="22" max="22" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3565,7 +3535,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>22</v>
       </c>
@@ -3615,7 +3585,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="3" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -3646,12 +3616,8 @@
       <c r="R3" t="s">
         <v>43</v>
       </c>
-      <c r="X3">
-        <f>COUNTIF(Table1[ManaValue],"&gt;1.0")</f>
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>44</v>
       </c>
@@ -3707,7 +3673,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>58</v>
       </c>
@@ -3738,12 +3704,8 @@
       <c r="Q5" t="s">
         <v>35</v>
       </c>
-      <c r="X5">
-        <f>COUNTIF(Table1[Rarity],"Mythic")</f>
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>62</v>
       </c>
@@ -3781,7 +3743,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="7" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>70</v>
       </c>
@@ -3822,7 +3784,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="8" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>78</v>
       </c>
@@ -3854,7 +3816,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>81</v>
       </c>
@@ -3886,7 +3848,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>85</v>
       </c>
@@ -3921,7 +3883,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="11" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>90</v>
       </c>
@@ -3956,7 +3918,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="12" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>96</v>
       </c>
@@ -4000,7 +3962,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>105</v>
       </c>
@@ -4056,7 +4018,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>118</v>
       </c>
@@ -4091,7 +4053,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>123</v>
       </c>
@@ -4123,7 +4085,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:24" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>127</v>
       </c>
@@ -4421,7 +4383,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="24" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>171</v>
       </c>
@@ -4480,7 +4442,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="25" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>185</v>
       </c>
@@ -4589,7 +4551,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>205</v>
       </c>
@@ -4639,7 +4601,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>213</v>
       </c>
@@ -4689,7 +4651,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="29" spans="1:22" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>219</v>
       </c>
@@ -5059,7 +5021,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="37" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>278</v>
       </c>
@@ -5156,7 +5118,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="39" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>295</v>
       </c>
@@ -5212,7 +5174,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="40" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>307</v>
       </c>
@@ -5268,7 +5230,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>315</v>
       </c>
@@ -5321,7 +5283,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>318</v>
       </c>
@@ -5430,7 +5392,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="44" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>334</v>
       </c>
@@ -5486,7 +5448,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="45" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>344</v>
       </c>
@@ -5851,7 +5813,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="52" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>401</v>
       </c>
@@ -5957,7 +5919,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="54" spans="1:21" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>417</v>
       </c>
@@ -6323,6 +6285,12 @@
       </c>
       <c r="T60" t="s">
         <v>473</v>
+      </c>
+    </row>
+    <row r="65" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M65">
+        <f>COUNTIF(Table1[RulesText],"*+1/+1 counter*")</f>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -6338,7 +6306,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54A5B80D-4AAC-4213-A401-1C1C355E7267}">
-  <dimension ref="A1:AA23"/>
+  <dimension ref="A1:AA33"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.5703125" bestFit="1" customWidth="1"/>
@@ -6353,7 +6321,7 @@
     <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="28" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.7109375" customWidth="1"/>
+    <col min="13" max="13" width="39.7109375" customWidth="1"/>
     <col min="14" max="14" width="13" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="38.140625" bestFit="1" customWidth="1"/>
@@ -6595,7 +6563,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>205</v>
       </c>
@@ -6775,7 +6743,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>295</v>
       </c>
@@ -6846,7 +6814,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="8" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>307</v>
       </c>
@@ -6917,7 +6885,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>315</v>
       </c>
@@ -6985,7 +6953,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>318</v>
       </c>
@@ -7553,7 +7521,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="18" spans="1:26" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>417</v>
       </c>
@@ -7956,6 +7924,12 @@
       </c>
       <c r="Y23" t="s">
         <v>473</v>
+      </c>
+    </row>
+    <row r="33" spans="13:13" x14ac:dyDescent="0.25">
+      <c r="M33">
+        <f>COUNTIF(Table4[RulesText],"*+1/+1 counter*")</f>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
